--- a/data/reports/risk_weekly_20260615-20260621.xlsx
+++ b/data/reports/risk_weekly_20260615-20260621.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19 07:40:14</t>
+          <t>2026-06-19 08:04:27</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -940,10 +940,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>86.04%</t>
+          <t>84.29%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7.42%</t>
+          <t>6.72%</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>81.06999999999999</v>
+        <v>67.58</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>87.76000000000001</v>
+        <v>94.95</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.74</v>
+        <v>1.06</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>79.19</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>94.61</v>
+        <v>92.75</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1.31</v>
+        <v>3.71</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>3</v>
@@ -1072,19 +1072,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>88.42999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>92.30000000000001</v>
+        <v>87.64999999999999</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>75.75</v>
+        <v>67.2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>95.67</v>
+        <v>86.33</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.2</v>
+        <v>3.67</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>70.06</v>
+        <v>74.61</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>86.04000000000001</v>
+        <v>84.28999999999999</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7.42</v>
+        <v>6.72</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>80.19</v>
+        <v>82.67999999999999</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>87.38</v>
+        <v>94.67999999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>83.98</v>
+        <v>72.55</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>91.03</v>
+        <v>89.71000000000001</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.86</v>
+        <v>2.43</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>78.77</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1.83</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="3">
@@ -1291,16 +1291,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>84.01000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4.74</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="4">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>92.88</v>
+        <v>77.92</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4.36</v>
+        <v>2.47</v>
       </c>
     </row>
   </sheetData>

--- a/data/reports/risk_weekly_20260615-20260621.xlsx
+++ b/data/reports/risk_weekly_20260615-20260621.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19 08:04:27</t>
+          <t>2026-06-19 08:38:58</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -940,10 +940,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>84.29%</t>
+          <t>86.50%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6.72%</t>
+          <t>4.64%</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>67.58</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>94.95</v>
+        <v>85.95</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.06</v>
+        <v>3.93</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>82.47</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>92.75</v>
+        <v>96.63000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3.71</v>
+        <v>2.17</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -1072,19 +1072,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>82.38</v>
+        <v>88.08</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>87.64999999999999</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.64</v>
+        <v>2.41</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>67.2</v>
+        <v>87.78</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>86.33</v>
+        <v>92.81</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.67</v>
+        <v>2.17</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>74.61</v>
+        <v>74.87</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>84.28999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6.72</v>
+        <v>4.64</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>1</v>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>82.67999999999999</v>
+        <v>88.66000000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>94.67999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.04</v>
+        <v>2.28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>1</v>
@@ -1160,16 +1160,16 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>72.55</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>89.71000000000001</v>
+        <v>95.14</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2.43</v>
+        <v>1.58</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>90.51000000000001</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.89</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="3">
@@ -1291,16 +1291,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>84.45</v>
+        <v>76.3</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4.59</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="4">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>77.92</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2.47</v>
+        <v>4.19</v>
       </c>
     </row>
   </sheetData>
